--- a/artfynd/A 64803-2023 artfynd.xlsx
+++ b/artfynd/A 64803-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64803-2023 artfynd.xlsx
+++ b/artfynd/A 64803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>17229520</v>
       </c>
       <c r="B2" t="n">
-        <v>85488</v>
+        <v>85489</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64803-2023 artfynd.xlsx
+++ b/artfynd/A 64803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>17229520</v>
       </c>
       <c r="B2" t="n">
-        <v>85489</v>
+        <v>85494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64803-2023 artfynd.xlsx
+++ b/artfynd/A 64803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>17229520</v>
       </c>
       <c r="B2" t="n">
-        <v>85494</v>
+        <v>85498</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64803-2023 artfynd.xlsx
+++ b/artfynd/A 64803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>17229520</v>
       </c>
       <c r="B2" t="n">
-        <v>85498</v>
+        <v>85503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>1081</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Gullmurkling</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 64803-2023 artfynd.xlsx
+++ b/artfynd/A 64803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>17229520</v>
       </c>
       <c r="B2" t="n">
-        <v>85503</v>
+        <v>85507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>1081</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Gullmurkling</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 64803-2023 artfynd.xlsx
+++ b/artfynd/A 64803-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17229520</v>
+        <v>103254786</v>
       </c>
       <c r="B2" t="n">
-        <v>85507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullmurkling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neolecta vitellina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Korf &amp; J.K.Rogers</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Änganäs, Pi lm</t>
+          <t>Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622743</v>
+        <v>622747</v>
       </c>
       <c r="R2" t="n">
-        <v>7308269</v>
+        <v>7307795</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-20</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-20</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,34 +764,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Sandra Laestander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Sandra Laestander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103254786</v>
+        <v>17229520</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>86476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,47 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gullmurkling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neolecta vitellina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bres.) Korf &amp; J.K.Rogers</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arjeplog, Pi lm</t>
+          <t>Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622746.9920813116</v>
+        <v>622743</v>
       </c>
       <c r="R3" t="n">
-        <v>7307794.538576025</v>
+        <v>7308269</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,22 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,33 +863,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sandra Laestander</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sandra Laestander</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103254762</v>
+        <v>103254731</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,33 +893,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622635.0955868576</v>
+        <v>622655</v>
       </c>
       <c r="R4" t="n">
-        <v>7307858.998770141</v>
+        <v>7307868</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,19 +951,9 @@
           <t>2022-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103254731</v>
+        <v>103254762</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,24 +991,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,13 +1025,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622655.2031201605</v>
+        <v>622635</v>
       </c>
       <c r="R5" t="n">
-        <v>7307868.466542396</v>
+        <v>7307859</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,19 +1058,9 @@
           <t>2022-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 64803-2023 artfynd.xlsx
+++ b/artfynd/A 64803-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103254786</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17229520</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103254731</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103254762</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>